--- a/bulls/lists/2026-10-05_bulls_launch/Bulls_3_offers_2026-10-05.xlsx
+++ b/bulls/lists/2026-10-05_bulls_launch/Bulls_3_offers_2026-10-05.xlsx
@@ -1,212 +1,165 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/talibachar/Downloads/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6C0E7DFC-20FE-4347-86D3-D34AA0E8F806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="2300" yWindow="2320" windowWidth="26840" windowHeight="15940" xr2:uid="{CA9469F0-2CD3-C048-BC6F-6F03AD83FF18}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2300" yWindow="2320" windowWidth="26840" windowHeight="15940" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="2026-08-14_NYJL_-_CJ_-_RDV_-_NY" sheetId="1" r:id="rId1"/>
+    <sheet name="2026-10-05_Intango" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2026-10-05_digidip" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
-  <si>
-    <t>Brand</t>
-  </si>
-  <si>
-    <t>Geos</t>
-  </si>
-  <si>
-    <t>Pure domain</t>
-  </si>
-  <si>
-    <t>Offer link</t>
-  </si>
-  <si>
-    <t>Blog url</t>
-  </si>
-  <si>
-    <t>Affiliate Network</t>
-  </si>
-  <si>
-    <t>Service Credential Name</t>
-  </si>
-  <si>
-    <t>AliExpress </t>
-  </si>
-  <si>
-    <t>US</t>
-  </si>
-  <si>
-    <t>aliexpress.com</t>
-  </si>
-  <si>
-    <t>https://www.dpbolvw.net/click-101728922-17242061</t>
-  </si>
-  <si>
-    <t>https://www.cyber-artical.com/</t>
-  </si>
-  <si>
-    <t>CJ</t>
-  </si>
-  <si>
-    <t>NYJL - CJ - RDV - NY</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
-    <font>
-      <sz val="12"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="19">
+    <font>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+      <color theme="3"/>
       <sz val="18"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <b val="1"/>
       <color theme="3"/>
-      <name val="Aptos Display"/>
-      <family val="2"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
       <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <b val="1"/>
       <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <b val="1"/>
       <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <color rgb="FF006100"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <color rgb="FF9C0006"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <color rgb="FF9C5700"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <color rgb="FF3F3F76"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <b val="1"/>
       <color rgb="FF3F3F3F"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <b val="1"/>
       <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <b val="1"/>
       <color theme="0"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="12"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <i val="1"/>
       <color rgb="FF7F7F7F"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <color theme="0"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <sz val="12"/>
     </font>
   </fonts>
-  <fills count="33">
-    <fill>
-      <patternFill patternType="none"/>
+  <fills count="34">
+    <fill>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -253,19 +206,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
+        <fgColor theme="4" tint="0.7999816888943144"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.5999938962981048"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.3999755851924192"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -276,19 +229,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
+        <fgColor theme="5" tint="0.7999816888943144"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.5999938962981048"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.3999755851924192"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -299,19 +252,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
+        <fgColor theme="6" tint="0.7999816888943144"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.5999938962981048"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.3999755851924192"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -322,19 +275,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
+        <fgColor theme="7" tint="0.7999816888943144"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.5999938962981048"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.3999755851924192"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -345,19 +298,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
+        <fgColor theme="8" tint="0.7999816888943144"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.5999938962981048"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.3999755851924192"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -368,20 +321,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <fgColor theme="9" tint="0.7999816888943144"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.5999938962981048"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.3999755851924192"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -416,7 +374,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.39997558519241921"/>
+        <color theme="4" tint="0.3999755851924192"/>
       </bottom>
       <diagonal/>
     </border>
@@ -502,107 +460,218 @@
     </border>
   </borders>
   <cellStyleXfs count="42">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="42">
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19"/>
+    <cellStyle name="Good" xfId="6" builtinId="26"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28"/>
+    <cellStyle name="Input" xfId="9" builtinId="20"/>
+    <cellStyle name="Output" xfId="10" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11"/>
+    <cellStyle name="Note" xfId="15" builtinId="10"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53"/>
+    <cellStyle name="Total" xfId="17" builtinId="25"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Claude</author>
+  </authors>
+  <commentList>
+    <comment ref="E2" authorId="0" shapeId="0">
+      <text>
+        <t>Pending: Elite Reads article is being written. Add the article URL when published.</t>
+      </text>
+    </comment>
+    <comment ref="G2" authorId="0" shapeId="0">
+      <text>
+        <t>Pending: Service Credential Name not provided yet (example format: 'NYJL - CJ - RDV - NY').</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Claude</author>
+  </authors>
+  <commentList>
+    <comment ref="E2" authorId="0" shapeId="0">
+      <text>
+        <t>Pending: Elite Reads article is being written. Add the article URL when published.</t>
+      </text>
+    </comment>
+    <comment ref="G2" authorId="0" shapeId="0">
+      <text>
+        <t>Pending: Service Credential Name not provided yet (example format: 'NYJL - CJ - RDV - NY').</t>
+      </text>
+    </comment>
+    <comment ref="E3" authorId="0" shapeId="0">
+      <text>
+        <t>Pending: Elite Reads article is being written. Add the article URL when published.</t>
+      </text>
+    </comment>
+    <comment ref="G3" authorId="0" shapeId="0">
+      <text>
+        <t>Pending: Service Credential Name not provided yet (example format: 'NYJL - CJ - RDV - NY').</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -921,57 +990,198 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2781299D-7CA0-2747-AEFB-C1C1691C1091}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col width="60" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Geos</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Pure domain</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Offer link</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Blog url</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Affiliate Network</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Service Credential Name</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>ncl.com</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>https://quxfjrw.com/adServe/aff?cmpid=703649&amp;pid=458124&amp;ap1=458124&amp;dp1=458124&amp;dp2=elite-reads.com&amp;dlink=https%3A%2F%2Fwww.ncl.com</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>Intango</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col width="60" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Geos</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Pure domain</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Offer link</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Blog url</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Affiliate Network</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Service Credential Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>waipu.tv</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>waipu.tv</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>https://3425.digidip.net/visit?url=https%3A%2F%2Fwww.waipu.tv&amp;currurl=https%3A%2F%2Felite-reads.com&amp;ref={clickid}</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>digidip</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>sky.de</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>sky.de</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>https://3425.digidip.net/visit?url=https%3A%2F%2Fwww.sky.de&amp;currurl=https%3A%2F%2Felite-reads.com&amp;ref={clickid}</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>digidip</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/bulls/lists/2026-10-05_bulls_launch/Bulls_3_offers_2026-10-05.xlsx
+++ b/bulls/lists/2026-10-05_bulls_launch/Bulls_3_offers_2026-10-05.xlsx
@@ -630,11 +630,6 @@
     <author>Claude</author>
   </authors>
   <commentList>
-    <comment ref="E2" authorId="0" shapeId="0">
-      <text>
-        <t>Pending: Elite Reads article is being written. Add the article URL when published.</t>
-      </text>
-    </comment>
     <comment ref="G2" authorId="0" shapeId="0">
       <text>
         <t>Pending: Service Credential Name not provided yet (example format: 'NYJL - CJ - RDV - NY').</t>
@@ -650,19 +645,9 @@
     <author>Claude</author>
   </authors>
   <commentList>
-    <comment ref="E2" authorId="0" shapeId="0">
-      <text>
-        <t>Pending: Elite Reads article is being written. Add the article URL when published.</t>
-      </text>
-    </comment>
     <comment ref="G2" authorId="0" shapeId="0">
       <text>
         <t>Pending: Service Credential Name not provided yet (example format: 'NYJL - CJ - RDV - NY').</t>
-      </text>
-    </comment>
-    <comment ref="E3" authorId="0" shapeId="0">
-      <text>
-        <t>Pending: Elite Reads article is being written. Add the article URL when published.</t>
       </text>
     </comment>
     <comment ref="G3" authorId="0" shapeId="0">
@@ -1059,7 +1044,11 @@
           <t>https://quxfjrw.com/adServe/aff?cmpid=703649&amp;pid=458124&amp;ap1=458124&amp;dp1=458124&amp;dp2=elite-reads.com&amp;dlink=https%3A%2F%2Fwww.ncl.com</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n"/>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>https://www.elite-reads.com/norwegian-cruise-line-ships-guide/</t>
+        </is>
+      </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
           <t>Intango</t>
@@ -1143,7 +1132,11 @@
           <t>https://3425.digidip.net/visit?url=https%3A%2F%2Fwww.waipu.tv&amp;currurl=https%3A%2F%2Felite-reads.com&amp;ref={clickid}</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n"/>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>https://www.elite-reads.com/waipu-tv-german-tv-streaming/</t>
+        </is>
+      </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
           <t>digidip</t>
@@ -1154,25 +1147,29 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
+          <t>Sky Deutschland</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
           <t>sky.de</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>sky.de</t>
-        </is>
-      </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
           <t>https://3425.digidip.net/visit?url=https%3A%2F%2Fwww.sky.de&amp;currurl=https%3A%2F%2Felite-reads.com&amp;ref={clickid}</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n"/>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>https://www.elite-reads.com/sky-deutschland-packages-worth-it/</t>
+        </is>
+      </c>
       <c r="F3" s="1" t="inlineStr">
         <is>
           <t>digidip</t>

--- a/bulls/lists/2026-10-05_bulls_launch/Bulls_3_offers_2026-10-05.xlsx
+++ b/bulls/lists/2026-10-05_bulls_launch/Bulls_3_offers_2026-10-05.xlsx
@@ -6,8 +6,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2300" yWindow="2320" windowWidth="26840" windowHeight="15940" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="2026-10-05_Intango" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2026-10-05_digidip" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2026-10-05" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -635,22 +634,12 @@
         <t>Pending: Service Credential Name not provided yet (example format: 'NYJL - CJ - RDV - NY').</t>
       </text>
     </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Claude</author>
-  </authors>
-  <commentList>
-    <comment ref="G2" authorId="0" shapeId="0">
+    <comment ref="G3" authorId="0" shapeId="0">
       <text>
         <t>Pending: Service Credential Name not provided yet (example format: 'NYJL - CJ - RDV - NY').</t>
       </text>
     </comment>
-    <comment ref="G3" authorId="0" shapeId="0">
+    <comment ref="G4" authorId="0" shapeId="0">
       <text>
         <t>Pending: Service Credential Name not provided yet (example format: 'NYJL - CJ - RDV - NY').</t>
       </text>
@@ -980,7 +969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="60" customWidth="1" min="4" max="4"/>
@@ -1056,126 +1045,71 @@
       </c>
       <c r="G2" s="2" t="n"/>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
-  <cols>
-    <col width="60" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Brand</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Geos</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Pure domain</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Offer link</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Blog url</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Affiliate Network</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Service Credential Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>waipu.tv</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>waipu.tv</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>https://3425.digidip.net/visit?url=https%3A%2F%2Fwww.waipu.tv&amp;currurl=https%3A%2F%2Felite-reads.com&amp;ref={clickid}</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>https://www.elite-reads.com/waipu-tv-german-tv-streaming/</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>digidip</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="n"/>
-    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
+          <t>waipu.tv</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>waipu.tv</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>https://3425.digidip.net/visit?url=https%3A%2F%2Fwww.waipu.tv&amp;currurl=https%3A%2F%2Felite-reads.com&amp;ref={clickid}</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>https://www.elite-reads.com/waipu-tv-german-tv-streaming/</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>digidip</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
           <t>Sky Deutschland</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>sky.de</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>https://3425.digidip.net/visit?url=https%3A%2F%2Fwww.sky.de&amp;currurl=https%3A%2F%2Felite-reads.com&amp;ref={clickid}</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>https://www.elite-reads.com/sky-deutschland-packages-worth-it/</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>digidip</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/bulls/lists/2026-10-05_bulls_launch/Bulls_3_offers_2026-10-05.xlsx
+++ b/bulls/lists/2026-10-05_bulls_launch/Bulls_3_offers_2026-10-05.xlsx
@@ -621,31 +621,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Claude</author>
-  </authors>
-  <commentList>
-    <comment ref="G2" authorId="0" shapeId="0">
-      <text>
-        <t>Pending: Service Credential Name not provided yet (example format: 'NYJL - CJ - RDV - NY').</t>
-      </text>
-    </comment>
-    <comment ref="G3" authorId="0" shapeId="0">
-      <text>
-        <t>Pending: Service Credential Name not provided yet (example format: 'NYJL - CJ - RDV - NY').</t>
-      </text>
-    </comment>
-    <comment ref="G4" authorId="0" shapeId="0">
-      <text>
-        <t>Pending: Service Credential Name not provided yet (example format: 'NYJL - CJ - RDV - NY').</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1043,7 +1018,11 @@
           <t>Intango</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n"/>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>NYJL - Intango - RDV - NY</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1076,7 +1055,11 @@
           <t>digidip</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n"/>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>NYJL - digidip - RDV - NY</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1109,10 +1092,13 @@
           <t>digidip</t>
         </is>
       </c>
-      <c r="G4" s="2" t="n"/>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>NYJL - digidip - RDV - NY</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>